--- a/data/trans_camb/IP16A09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 4,24</t>
+          <t>-9,66; 4,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 2,58</t>
+          <t>-12,18; 2,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 6,36</t>
+          <t>-9,23; 6,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 0,0</t>
+          <t>-15,7; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,1</t>
+          <t>-7,45; 3,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -0,26</t>
+          <t>-9,64; -0,11</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 398,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,98; 259,23</t>
+          <t>-81,94; 176,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 2,95</t>
+          <t>-9,45; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 1,86</t>
+          <t>-9,8; 2,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 3,81</t>
+          <t>-2,98; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,0</t>
+          <t>-6,39; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 2,27</t>
+          <t>-4,72; 2,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,52</t>
+          <t>-5,52; 0,75</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,46; 189,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,39</t>
+          <t>-100,0; 169,79</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 0,0</t>
+          <t>-13,34; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 0,0</t>
+          <t>-13,34; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 0,0</t>
+          <t>-13,72; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 11,85</t>
+          <t>-4,09; 11,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 0,0</t>
+          <t>-9,62; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 5,53</t>
+          <t>-4,19; 4,89</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 0,0</t>
+          <t>-12,92; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 2,98</t>
+          <t>-10,27; 3,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 13,61</t>
+          <t>-1,42; 13,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 0,0</t>
+          <t>-8,18; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 4,76</t>
+          <t>-3,49; 5,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 0,87</t>
+          <t>-5,97; 0,86</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,45</t>
+          <t>-5,9; 0,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,06</t>
+          <t>-6,52; -0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,39</t>
+          <t>-2,29; 3,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,4</t>
+          <t>-2,8; 2,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,4</t>
+          <t>-2,91; 1,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,33</t>
+          <t>-3,68; 0,22</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 40,28</t>
+          <t>-90,45; 37,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-91,77; 34,91</t>
+          <t>-92,46; 5,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 412,25</t>
+          <t>-63,48; 394,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,91; 312,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,8; 67,46</t>
+          <t>-65,08; 81,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 29,26</t>
+          <t>-80,72; 24,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 4,52</t>
+          <t>-10,94; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 2,39</t>
+          <t>-11,22; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 6,36</t>
+          <t>-9,06; 6,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 0,0</t>
+          <t>-15,79; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 3,88</t>
+          <t>-6,66; 4,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,64; -0,11</t>
+          <t>-9,36; 0,04</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 398,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,94; 176,86</t>
+          <t>-83,99; 257,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 2,93</t>
+          <t>-10,7; 2,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 2,1</t>
+          <t>-11,08; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,9</t>
+          <t>-2,95; 4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 0,0</t>
+          <t>-6,85; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,41</t>
+          <t>-4,81; 2,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,75</t>
+          <t>-5,54; 0,64</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,89; 303,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,79</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 0,0</t>
+          <t>-12,13; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 0,0</t>
+          <t>-12,13; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 0,0</t>
+          <t>-14,87; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 11,46</t>
+          <t>-5,91; 11,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,0</t>
+          <t>-8,99; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,89</t>
+          <t>-4,59; 4,85</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 0,0</t>
+          <t>-10,59; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,02</t>
+          <t>-10,27; 3,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 13,61</t>
+          <t>-1,34; 13,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,0</t>
+          <t>-9,39; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,42</t>
+          <t>-3,49; 4,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,86</t>
+          <t>-5,38; 0,87</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,48</t>
+          <t>-5,82; 0,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -0,37</t>
+          <t>-6,33; -0,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,57</t>
+          <t>-2,25; 3,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,39</t>
+          <t>-2,73; 2,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,36</t>
+          <t>-2,85; 1,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,22</t>
+          <t>-3,73; 0,34</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 37,26</t>
+          <t>-88,98; 41,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 5,9</t>
+          <t>-92,51; 23,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,48; 394,01</t>
+          <t>-65,21; 446,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-84,91; 312,38</t>
+          <t>-82,4; 329,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 81,24</t>
+          <t>-66,28; 71,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 24,51</t>
+          <t>-81,13; 33,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Edad-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-3,42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,32</t>
+          <t>-10,28; 6,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 2,38</t>
+          <t>-15,8; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 6,72</t>
+          <t>-10,09; 4,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 0,0</t>
+          <t>-11,36; 2,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,11</t>
+          <t>-6,18; 4,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 0,04</t>
+          <t>-9,53; -0,26</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-2,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-32,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-63,58%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,72%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,99; 257,2</t>
+          <t>-81,98; 259,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,27</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-3,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 2,75</t>
+          <t>-3,81; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 1,92</t>
+          <t>-6,4; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,24</t>
+          <t>-9,31; 2,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,0</t>
+          <t>-9,91; 1,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,28</t>
+          <t>-4,56; 2,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,64</t>
+          <t>-5,66; 0,52</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-50,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-58,95%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>49,29%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,89; 303,21</t>
+          <t>-89,46; 189,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 145,39</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,83</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-2,34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-2,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 0,0</t>
+          <t>-14,99; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 0,0</t>
+          <t>-5,75; 11,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 0,0</t>
+          <t>-12,22; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 11,47</t>
+          <t>-12,22; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 0,0</t>
+          <t>-8,95; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 4,85</t>
+          <t>-4,31; 5,53</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>141,09%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>141,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,63</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-1,11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 0,0</t>
+          <t>-1,34; 13,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,0</t>
+          <t>-8,23; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 13,83</t>
+          <t>-12,73; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 0,0</t>
+          <t>-10,34; 2,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,74</t>
+          <t>-3,39; 4,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,87</t>
+          <t>-5,37; 0,87</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>258,26%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-42,61%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>258,26%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-2,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-2,75</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,44</t>
+          <t>-2,21; 3,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -0,15</t>
+          <t>-3,09; 2,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,39</t>
+          <t>-5,45; 0,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,38</t>
+          <t>-6,23; 0,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,33</t>
+          <t>-2,98; 1,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,34</t>
+          <t>-3,62; 0,33</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-16,9%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-54,86%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-66,23%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-16,9%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,98; 41,58</t>
+          <t>-62,65; 412,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,51; 23,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 446,31</t>
+          <t>-87,28; 40,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 329,39</t>
+          <t>-91,77; 34,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,28; 71,83</t>
+          <t>-65,8; 67,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,13; 33,02</t>
+          <t>-81,86; 29,26</t>
         </is>
       </c>
     </row>
